--- a/table/Datas/__beans__.xlsx
+++ b/table/Datas/__beans__.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,6 +677,86 @@
       <c r="L12" t="inlineStr">
         <is>
           <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>가격 한 줄</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>currency_id</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ReasonCap</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>사유별 일일 상한</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>currency_id</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>long</t>
         </is>
       </c>
     </row>

--- a/table/Datas/__beans__.xlsx
+++ b/table/Datas/__beans__.xlsx
@@ -691,6 +691,11 @@
           <t>가격 한 줄</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>c,l</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>currency_id</t>
@@ -723,6 +728,11 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>사유별 일일 상한</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>c,l</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">

--- a/table/Datas/__beans__.xlsx
+++ b/table/Datas/__beans__.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -765,6 +765,45 @@
         </is>
       </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>StatCoin</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>결과 지표 한 번당 코인</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stat_key</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>coins</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>long</t>
         </is>

--- a/table/Datas/__beans__.xlsx
+++ b/table/Datas/__beans__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,6 +804,120 @@
         </is>
       </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>QuestClause</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>퀘스트 조건 한 줄(키 연산 값)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>op</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>QuestReward</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>퀘스트 난이도별 보상</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>period</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>coins</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>xp</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>long</t>
         </is>
